--- a/tiflow-diga/build/0.9.0/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
+++ b/tiflow-diga/build/0.9.0/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="352">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow/diga/StructureDefinition/GEM-ERP-PR-Communication-DiGA</t>
+    <t>https://gematik.de/fhir/tiflow/diga/StructureDefinition/GEM_ERP_PR_Communication_DiGA</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06</t>
+    <t>2025-09-25</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,6 +439,136 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Communication.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Communication.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Unique identifier</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this communication by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Communication.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>Communication.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Communication.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Task) &lt;&lt;referenced&gt;&gt;
+</t>
+  </si>
+  <si>
+    <t>Gibt das E-Rezept-Token gemäß gemSpec_DM_eRp an.</t>
+  </si>
+  <si>
+    <t>An order, proposal or plan fulfilled in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -447,153 +577,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Communication.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Communication.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Unique identifier</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this communication by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
-    <t>Communication.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
-    <t>Event.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>Communication.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Communication.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Task) &lt;&lt;referenced&gt;&gt;
-</t>
-  </si>
-  <si>
-    <t>Gibt das E-Rezept-Token gemäß gemSpec_DM_eRp an.</t>
-  </si>
-  <si>
-    <t>An order, proposal or plan fulfilled in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
-    <t>Communication.basedOn.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Communication.basedOn.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -690,9 +673,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -771,9 +751,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -826,9 +803,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1142,13 +1116,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1473,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2475,19 +2443,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2499,7 +2467,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2513,10 +2481,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2542,16 +2510,16 @@
         <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2588,19 +2556,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2612,7 +2580,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2626,10 +2594,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2652,19 +2620,19 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2713,7 +2681,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2722,27 +2690,27 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2753,7 +2721,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2765,17 +2733,15 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2824,7 +2790,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2839,21 +2805,21 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2864,7 +2830,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -2879,13 +2845,13 @@
         <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2935,7 +2901,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2950,25 +2916,25 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2987,16 +2953,16 @@
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3046,7 +3012,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3055,27 +3021,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3098,13 +3064,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3155,7 +3121,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3176,15 +3142,15 @@
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3213,7 +3179,7 @@
         <v>133</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>135</v>
@@ -3254,19 +3220,19 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3278,7 +3244,7 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>76</v>
@@ -3287,15 +3253,15 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3318,16 +3284,16 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3377,7 +3343,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3386,7 +3352,7 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
@@ -3403,10 +3369,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3432,13 +3398,13 @@
         <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3464,13 +3430,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3488,7 +3454,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3514,10 +3480,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3540,16 +3506,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3599,7 +3565,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3608,7 +3574,7 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>98</v>
@@ -3620,15 +3586,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3651,16 +3617,16 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3710,7 +3676,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3736,21 +3702,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -3762,17 +3728,15 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3821,7 +3785,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3830,27 +3794,27 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3861,7 +3825,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -3873,17 +3837,15 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3932,7 +3894,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3941,10 +3903,10 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3953,15 +3915,15 @@
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3987,13 +3949,13 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4001,7 +3963,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>76</v>
@@ -4019,13 +3981,13 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
@@ -4043,7 +4005,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -4058,10 +4020,10 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4069,21 +4031,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -4095,16 +4057,16 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4130,13 +4092,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4154,7 +4116,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4163,27 +4125,27 @@
         <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4194,7 +4156,7 @@
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4206,16 +4168,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4241,13 +4203,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4265,7 +4227,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4274,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
@@ -4283,18 +4245,18 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4305,7 +4267,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4320,20 +4282,20 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>76</v>
@@ -4354,13 +4316,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4378,7 +4340,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4396,7 +4358,7 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4404,10 +4366,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4418,7 +4380,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4430,17 +4392,15 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4465,13 +4425,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4489,7 +4449,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4498,7 +4458,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
@@ -4510,26 +4470,26 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4541,17 +4501,15 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4600,7 +4558,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4609,27 +4567,27 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4640,7 +4598,7 @@
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4652,16 +4610,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4687,13 +4645,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4711,7 +4669,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4720,7 +4678,7 @@
         <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>98</v>
@@ -4729,18 +4687,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4751,7 +4709,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -4763,16 +4721,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4822,7 +4780,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4831,27 +4789,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4862,7 +4820,7 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -4874,16 +4832,16 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4933,7 +4891,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4942,27 +4900,27 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4985,16 +4943,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5044,7 +5002,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5059,10 +5017,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5070,10 +5028,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5096,16 +5054,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="N33" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5155,7 +5113,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5170,10 +5128,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5181,10 +5139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5207,16 +5165,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5266,7 +5224,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5275,27 +5233,27 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5318,13 +5276,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5375,7 +5333,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5396,15 +5354,15 @@
         <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5433,7 +5391,7 @@
         <v>133</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>135</v>
@@ -5474,19 +5432,19 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5498,7 +5456,7 @@
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>76</v>
@@ -5507,15 +5465,15 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5538,16 +5496,16 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5597,7 +5555,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5606,7 +5564,7 @@
         <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>98</v>
@@ -5623,10 +5581,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5652,13 +5610,13 @@
         <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5684,13 +5642,13 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5708,7 +5666,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5732,12 +5690,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5751,7 +5709,7 @@
         <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>76</v>
@@ -5760,16 +5718,16 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5819,7 +5777,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5828,7 +5786,7 @@
         <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>98</v>
@@ -5840,15 +5798,15 @@
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5871,16 +5829,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5930,7 +5888,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5956,10 +5914,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5982,16 +5940,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6041,7 +5999,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6050,27 +6008,27 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6093,13 +6051,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6150,7 +6108,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6171,15 +6129,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6208,7 +6166,7 @@
         <v>133</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>135</v>
@@ -6249,19 +6207,19 @@
         <v>76</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6273,7 +6231,7 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
@@ -6282,15 +6240,15 @@
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6313,16 +6271,16 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6372,7 +6330,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6381,7 +6339,7 @@
         <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>98</v>
@@ -6398,10 +6356,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6427,13 +6385,13 @@
         <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6459,13 +6417,13 @@
         <v>76</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6483,7 +6441,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6509,10 +6467,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6535,16 +6493,16 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6594,7 +6552,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6603,7 +6561,7 @@
         <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>98</v>
@@ -6615,15 +6573,15 @@
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6646,16 +6604,16 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6705,7 +6663,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6731,10 +6689,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6745,7 +6703,7 @@
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -6757,16 +6715,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6792,13 +6750,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6816,7 +6774,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6825,27 +6783,27 @@
         <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6856,7 +6814,7 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>76</v>
@@ -6868,17 +6826,15 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -6927,7 +6883,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6936,27 +6892,27 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6979,13 +6935,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7036,7 +6992,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7045,7 +7001,7 @@
         <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>98</v>
@@ -7057,15 +7013,15 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>182</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7088,13 +7044,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7145,7 +7101,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7166,15 +7122,15 @@
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7203,7 +7159,7 @@
         <v>133</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>135</v>
@@ -7244,19 +7200,19 @@
         <v>76</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7268,7 +7224,7 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
@@ -7277,19 +7233,19 @@
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7311,16 +7267,16 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7369,7 +7325,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7381,7 +7337,7 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
@@ -7395,10 +7351,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7421,16 +7377,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7480,7 +7436,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>86</v>
@@ -7489,7 +7445,7 @@
         <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
@@ -7501,15 +7457,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>182</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7520,7 +7476,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>76</v>
@@ -7532,17 +7488,15 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7591,7 +7545,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7600,19 +7554,19 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>361</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
